--- a/jira_export_2026-09-14.xlsx
+++ b/jira_export_2026-09-14.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>19,142 €</t>
+          <t>23,173 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,14 +760,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>6,535 €</t>
+          <t>6,864 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>12,606 €</t>
+          <t>16,309 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>194 h</t>
+          <t>195 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P129"/>
+  <dimension ref="A1:P128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>726.05</v>
+        <v>1507.95</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
@@ -2321,10 +2321,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="P22" s="15" t="n">
-        <v>12.29</v>
+        <v>49.14</v>
       </c>
     </row>
     <row r="23">
@@ -3042,27 +3042,27 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
@@ -3093,19 +3093,19 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>707</v>
-      </c>
-      <c r="O33" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O33" s="12" t="n">
+        <v>177.5</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
@@ -3114,27 +3114,27 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
@@ -3165,19 +3165,19 @@
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="15" t="n">
-        <v>177.5</v>
+        <v>300</v>
+      </c>
+      <c r="O34" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P34" s="15" t="n">
         <v>0</v>
@@ -3186,27 +3186,27 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3221,69 +3221,69 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>300</v>
+        <v>510</v>
       </c>
       <c r="O35" s="16" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="P35" s="12" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3293,64 +3293,64 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>510</v>
-      </c>
-      <c r="O36" s="16" t="n">
-        <v>0</v>
+        <v>242.9</v>
+      </c>
+      <c r="O36" s="15" t="n">
+        <v>1242.9</v>
       </c>
       <c r="P36" s="15" t="n">
-        <v>0</v>
+        <v>621.45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3377,37 +3377,37 @@
         <v>3</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>242.9</v>
-      </c>
-      <c r="O37" s="12" t="n">
-        <v>1242.9</v>
+        <v>220</v>
+      </c>
+      <c r="O37" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>621.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -3442,44 +3442,44 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>220</v>
-      </c>
-      <c r="O38" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O38" s="15" t="n">
+        <v>65.73</v>
       </c>
       <c r="P38" s="15" t="n">
-        <v>0</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3521,52 +3521,52 @@
         <v>3</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="12" t="n">
-        <v>65.73</v>
+        <v>1890</v>
+      </c>
+      <c r="O39" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P39" s="12" t="n">
-        <v>43.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
@@ -3586,44 +3586,44 @@
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O40" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O40" s="15" t="n">
+        <v>465.85</v>
       </c>
       <c r="P40" s="15" t="n">
-        <v>0</v>
+        <v>93.17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3658,59 +3658,59 @@
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="12" t="n">
-        <v>266.2</v>
+        <v>920</v>
+      </c>
+      <c r="O41" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P41" s="12" t="n">
-        <v>53.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3737,37 +3737,37 @@
         <v>3</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>920</v>
-      </c>
-      <c r="O42" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O42" s="15" t="n">
+        <v>679.5</v>
       </c>
       <c r="P42" s="15" t="n">
-        <v>0</v>
+        <v>906</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3813,53 +3813,53 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>679.5</v>
+        <v>540</v>
       </c>
       <c r="P43" s="12" t="n">
-        <v>906</v>
+        <v>720</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3869,64 +3869,64 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>540</v>
+        <v>505</v>
       </c>
       <c r="P44" s="15" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
@@ -3953,23 +3953,23 @@
         <v>3</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
@@ -3978,12 +3978,12 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4013,69 +4013,69 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0</v>
+        <v>691.9</v>
       </c>
       <c r="P46" s="15" t="n">
-        <v>0</v>
+        <v>461.27</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4085,69 +4085,69 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="12" t="n">
-        <v>691.9</v>
+        <v>171.4</v>
+      </c>
+      <c r="O47" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>461.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
@@ -4173,19 +4173,19 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O48" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O48" s="15" t="n">
+        <v>3339.2</v>
       </c>
       <c r="P48" s="15" t="n">
         <v>0</v>
@@ -4194,27 +4194,27 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4245,19 +4245,19 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="12" t="n">
-        <v>3339.2</v>
+        <v>344</v>
+      </c>
+      <c r="O49" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>0</v>
@@ -4266,27 +4266,27 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
@@ -4317,16 +4317,16 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>344</v>
+        <v>500</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4338,27 +4338,27 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
@@ -4389,16 +4389,16 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>500</v>
+        <v>149</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4410,32 +4410,32 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4445,38 +4445,38 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>149</v>
+        <v>625</v>
       </c>
       <c r="O52" s="16" t="n">
-        <v>0</v>
+        <v>337.5</v>
       </c>
       <c r="P52" s="15" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
     </row>
     <row r="53">
@@ -4533,53 +4533,53 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>625</v>
-      </c>
-      <c r="O53" s="16" t="n">
-        <v>337.5</v>
+        <v>0</v>
+      </c>
+      <c r="O53" s="12" t="n">
+        <v>16</v>
       </c>
       <c r="P53" s="12" t="n">
-        <v>540</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4589,49 +4589,49 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="15" t="n">
-        <v>16</v>
+        <v>910</v>
+      </c>
+      <c r="O54" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P54" s="15" t="n">
-        <v>25.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4666,27 +4666,27 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>910</v>
+        <v>1207</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4698,32 +4698,32 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4733,32 +4733,32 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>1207</v>
+        <v>500</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4770,32 +4770,32 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -4817,57 +4817,57 @@
         <v>5</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="O57" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O57" s="12" t="n">
+        <v>1400</v>
       </c>
       <c r="P57" s="12" t="n">
-        <v>0</v>
+        <v>466.67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4877,28 +4877,28 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
@@ -4914,12 +4914,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -4929,12 +4929,12 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4954,29 +4954,29 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="12" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="O59" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
@@ -4986,32 +4986,32 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5021,32 +5021,32 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K60" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>142.1</v>
+        <v>2335</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5058,32 +5058,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5093,34 +5093,34 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>2335</v>
-      </c>
-      <c r="O61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -5130,32 +5130,32 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -5165,28 +5165,28 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
@@ -5202,12 +5202,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5242,29 +5242,29 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="O63" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
@@ -5274,32 +5274,32 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -5309,69 +5309,69 @@
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>450</v>
+        <v>910</v>
       </c>
       <c r="O64" s="16" t="n">
-        <v>0</v>
+        <v>136.5</v>
       </c>
       <c r="P64" s="15" t="n">
-        <v>0</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5381,49 +5381,49 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>910</v>
+        <v>590.15</v>
       </c>
       <c r="O65" s="16" t="n">
-        <v>136.5</v>
+        <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
-        <v>68.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
@@ -5469,19 +5469,19 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>590.15</v>
-      </c>
-      <c r="O66" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O66" s="15" t="n">
+        <v>823.65</v>
       </c>
       <c r="P66" s="15" t="n">
         <v>0</v>
@@ -5490,12 +5490,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
@@ -5541,19 +5541,19 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="12" t="n">
-        <v>823.65</v>
+        <v>285</v>
+      </c>
+      <c r="O67" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P67" s="12" t="n">
         <v>0</v>
@@ -5562,32 +5562,32 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -5602,27 +5602,27 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>285</v>
+        <v>1325</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5634,12 +5634,12 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5674,27 +5674,27 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>1325</v>
+        <v>120</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5706,32 +5706,32 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
@@ -5757,16 +5757,16 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>120</v>
+        <v>588</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5778,12 +5778,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5818,59 +5818,59 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>588</v>
-      </c>
-      <c r="O71" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O71" s="12" t="n">
+        <v>1470</v>
       </c>
       <c r="P71" s="12" t="n">
-        <v>0</v>
+        <v>452.31</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5885,34 +5885,34 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O72" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
@@ -5922,12 +5922,12 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5957,12 +5957,12 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
@@ -5973,16 +5973,16 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>203.5</v>
+        <v>300</v>
       </c>
       <c r="O73" s="16" t="n">
         <v>0</v>
@@ -5994,32 +5994,32 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
@@ -6045,16 +6045,16 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6066,27 +6066,27 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -6106,29 +6106,29 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>700</v>
-      </c>
-      <c r="O75" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
@@ -6138,32 +6138,32 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6173,34 +6173,34 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="15" t="n">
+        <v>210</v>
+      </c>
+      <c r="O76" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="15" t="n">
@@ -6210,12 +6210,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6261,19 +6261,19 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="O77" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O77" s="12" t="n">
+        <v>281</v>
       </c>
       <c r="P77" s="12" t="n">
         <v>0</v>
@@ -6282,12 +6282,12 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
@@ -6333,19 +6333,19 @@
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="15" t="n">
-        <v>281</v>
+        <v>130</v>
+      </c>
+      <c r="O78" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
         <v>0</v>
@@ -6354,12 +6354,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
@@ -6405,16 +6405,16 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="O79" s="16" t="n">
         <v>0</v>
@@ -6426,12 +6426,12 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -6466,27 +6466,27 @@
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K80" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="O80" s="16" t="n">
         <v>0</v>
@@ -6498,32 +6498,32 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -6533,32 +6533,32 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>140</v>
+        <v>690</v>
       </c>
       <c r="O81" s="16" t="n">
         <v>0</v>
@@ -6570,27 +6570,27 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
@@ -6610,29 +6610,29 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>690</v>
-      </c>
-      <c r="O82" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="15" t="n">
@@ -6693,18 +6693,18 @@
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="12" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="O83" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -6765,16 +6765,16 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>187.5</v>
+        <v>787.5</v>
       </c>
       <c r="O84" s="16" t="n">
         <v>0</v>
@@ -6786,32 +6786,32 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6821,35 +6821,35 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>787.5</v>
-      </c>
-      <c r="O85" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O85" s="12" t="n">
+        <v>362.5</v>
       </c>
       <c r="P85" s="12" t="n">
         <v>0</v>
@@ -6858,32 +6858,30 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E86" s="14" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="n">
+        <v/>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -6893,35 +6891,35 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>362.5</v>
+        <v>0</v>
       </c>
       <c r="P86" s="15" t="n">
         <v>0</v>
@@ -6930,12 +6928,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6945,11 +6943,13 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E87" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
@@ -6968,23 +6968,23 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>2.75</v>
+        <v>0.95</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
@@ -7267,18 +7267,18 @@
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O91" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="12" t="n">
@@ -7288,12 +7288,12 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
@@ -7303,13 +7303,11 @@
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E92" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="n">
+        <v/>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
@@ -7323,34 +7321,34 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O92" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7360,12 +7358,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7375,48 +7373,34 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F93" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="inlineStr"/>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H93" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H93" s="11" t="inlineStr"/>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L93" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27642</t>
-        </is>
-      </c>
-      <c r="M93" s="11" t="inlineStr">
-        <is>
-          <t>00143935</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L93" s="11" t="inlineStr"/>
+      <c r="M93" s="11" t="inlineStr"/>
       <c r="N93" s="12" t="n">
         <v>0</v>
       </c>
@@ -7430,12 +7414,12 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
@@ -7445,34 +7429,48 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F94" s="14" t="inlineStr"/>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H94" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H94" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" s="14" t="inlineStr"/>
-      <c r="M94" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L94" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-26814</t>
+        </is>
+      </c>
+      <c r="M94" s="14" t="inlineStr">
+        <is>
+          <t>00142941</t>
+        </is>
+      </c>
       <c r="N94" s="15" t="n">
         <v>0</v>
       </c>
@@ -7486,12 +7484,12 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
@@ -7501,7 +7499,7 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7519,34 +7517,34 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="12" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O95" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="12" t="n">
@@ -7556,12 +7554,12 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
@@ -7571,7 +7569,7 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7594,44 +7592,44 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O96" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O96" s="15" t="n">
+        <v>416.188</v>
       </c>
       <c r="P96" s="15" t="n">
-        <v>0</v>
+        <v>277.46</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7641,11 +7639,13 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
@@ -7654,54 +7654,54 @@
       </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>13</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O97" s="12" t="n">
-        <v>416.188</v>
+        <v>0</v>
       </c>
       <c r="P97" s="12" t="n">
-        <v>277.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
@@ -7711,13 +7711,11 @@
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E98" s="14" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>VILLE DE BAGNOLET</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v/>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -7726,33 +7724,33 @@
       </c>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
@@ -7768,12 +7766,12 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7783,7 +7781,7 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7806,23 +7804,23 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
         <v>14</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>1.5</v>
+        <v>0.06</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
@@ -7887,12 +7885,12 @@
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
@@ -7923,7 +7921,7 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7957,12 +7955,12 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
@@ -7993,7 +7991,7 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -8027,12 +8025,12 @@
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
@@ -8048,12 +8046,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22126</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8063,7 +8061,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Métropole Européenne de Lille</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8081,28 +8079,28 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-27368</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>484163</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
@@ -8118,22 +8116,22 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22126</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>Métropole Européenne de Lille</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8156,29 +8154,29 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27368</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>484163</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O104" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="15" t="n">
@@ -8188,12 +8186,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8203,7 +8201,7 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8221,34 +8219,34 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O105" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8258,22 +8256,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8291,28 +8289,28 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
@@ -8328,22 +8326,22 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8366,29 +8364,29 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O107" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8398,12 +8396,12 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -8413,7 +8411,7 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
@@ -8436,29 +8434,29 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O108" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="15" t="n">
@@ -8468,22 +8466,22 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8501,28 +8499,28 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K109" s="11" t="n">
         <v>0.5</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
@@ -8587,12 +8585,12 @@
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-28214</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>458286</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
@@ -8608,12 +8606,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8623,7 +8621,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8636,35 +8634,27 @@
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L111" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28214</t>
-        </is>
-      </c>
-      <c r="M111" s="11" t="inlineStr">
-        <is>
-          <t>458286</t>
-        </is>
-      </c>
+        <v>5.5</v>
+      </c>
+      <c r="L111" s="11" t="inlineStr"/>
+      <c r="M111" s="11" t="inlineStr"/>
       <c r="N111" s="12" t="n">
         <v>0</v>
       </c>
@@ -8678,22 +8668,22 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8711,7 +8701,7 @@
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
@@ -8723,7 +8713,7 @@
         <v>21</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>5.5</v>
+        <v>5.58</v>
       </c>
       <c r="L112" s="14" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -8740,22 +8730,22 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8763,36 +8753,44 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
         <v>21</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="L113" s="11" t="inlineStr"/>
-      <c r="M113" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O113" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
@@ -8802,22 +8800,22 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
@@ -8825,7 +8823,7 @@
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G114" s="14" t="inlineStr">
@@ -8835,34 +8833,34 @@
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
         <v>21</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O114" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="15" t="n">
@@ -8887,7 +8885,7 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8921,7 +8919,7 @@
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
@@ -8942,12 +8940,12 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -8957,7 +8955,7 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -8987,22 +8985,22 @@
         <v>21</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O116" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="15" t="n">
@@ -9012,22 +9010,22 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9040,7 +9038,7 @@
       </c>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr">
@@ -9050,29 +9048,21 @@
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M117" s="11" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L117" s="11" t="inlineStr"/>
+      <c r="M117" s="11" t="inlineStr"/>
       <c r="N117" s="12" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O117" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="12" t="n">
@@ -9082,12 +9072,12 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
@@ -9097,7 +9087,7 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9115,19 +9105,19 @@
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>0.5</v>
+        <v>3.58</v>
       </c>
       <c r="L118" s="14" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -9144,22 +9134,22 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9172,27 +9162,35 @@
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="L119" s="11" t="inlineStr"/>
-      <c r="M119" s="11" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L119" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M119" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N119" s="12" t="n">
         <v>0</v>
       </c>
@@ -9206,22 +9204,22 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9234,35 +9232,23 @@
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H120" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H120" s="14" t="inlineStr"/>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L120" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M120" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L120" s="14" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
       <c r="N120" s="15" t="n">
         <v>0</v>
       </c>
@@ -9276,26 +9262,28 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[CD 14] Paramétrages</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
-        </is>
-      </c>
-      <c r="E121" s="11" t="n">
-        <v/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
@@ -9307,17 +9295,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H121" s="11" t="inlineStr"/>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L121" s="11" t="inlineStr"/>
       <c r="M121" s="11" t="inlineStr"/>
@@ -9334,27 +9326,23 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
-        </is>
-      </c>
-      <c r="C122" s="14" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="inlineStr"/>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F122" s="14" t="inlineStr">
@@ -9369,19 +9357,19 @@
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>0.25</v>
+        <v>2.75</v>
       </c>
       <c r="L122" s="14" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -9398,25 +9386,21 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr"/>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E123" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
-      </c>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr"/>
       <c r="F123" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9424,26 +9408,26 @@
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H123" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr"/>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L123" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L123" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
       <c r="M123" s="11" t="inlineStr"/>
       <c r="N123" s="12" t="n">
         <v>0</v>
@@ -9458,18 +9442,18 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1334</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr"/>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="E124" s="14" t="inlineStr"/>
@@ -9480,7 +9464,7 @@
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H124" s="14" t="inlineStr"/>
@@ -9493,13 +9477,9 @@
         <v>2</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L124" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L124" s="14" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
       <c r="N124" s="15" t="n">
         <v>0</v>
@@ -9514,18 +9494,18 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PSC-1334</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr"/>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr"/>
@@ -9536,23 +9516,31 @@
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr"/>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L125" s="11" t="inlineStr"/>
-      <c r="M125" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L125" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M125" s="11" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="N125" s="12" t="n">
         <v>0</v>
       </c>
@@ -9566,18 +9554,18 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr"/>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E126" s="14" t="inlineStr"/>
@@ -9594,23 +9582,23 @@
       <c r="H126" s="14" t="inlineStr"/>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>0.25</v>
+        <v>3.5</v>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34778</t>
+          <t>PDMDEP-33362</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>00172868</t>
+          <t>00167140</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
@@ -9626,18 +9614,18 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-668</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>VILLE DE DUGNY</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr"/>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>VILLE DE DUGNY</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr"/>
@@ -9648,31 +9636,23 @@
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr"/>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L127" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M127" s="11" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L127" s="11" t="inlineStr"/>
+      <c r="M127" s="11" t="inlineStr"/>
       <c r="N127" s="12" t="n">
         <v>0</v>
       </c>
@@ -9684,83 +9664,31 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="13" t="inlineStr">
-        <is>
-          <t>PSC-668</t>
-        </is>
-      </c>
-      <c r="B128" s="14" t="inlineStr">
-        <is>
-          <t>VILLE DE DUGNY</t>
-        </is>
-      </c>
-      <c r="C128" s="14" t="inlineStr"/>
-      <c r="D128" s="14" t="inlineStr">
-        <is>
-          <t>VILLE DE DUGNY</t>
-        </is>
-      </c>
-      <c r="E128" s="14" t="inlineStr"/>
-      <c r="F128" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G128" s="14" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H128" s="14" t="inlineStr"/>
-      <c r="I128" s="14" t="inlineStr">
-        <is>
-          <t>04/04/2025</t>
-        </is>
-      </c>
-      <c r="J128" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="K128" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L128" s="14" t="inlineStr"/>
-      <c r="M128" s="14" t="inlineStr"/>
-      <c r="N128" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="17" t="inlineStr">
+      <c r="A128" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B129" s="17" t="inlineStr"/>
-      <c r="C129" s="17" t="inlineStr"/>
-      <c r="D129" s="17" t="inlineStr"/>
-      <c r="E129" s="17" t="inlineStr"/>
-      <c r="F129" s="17" t="inlineStr"/>
-      <c r="G129" s="17" t="inlineStr"/>
-      <c r="H129" s="17" t="inlineStr"/>
-      <c r="I129" s="17" t="inlineStr"/>
-      <c r="J129" s="17" t="inlineStr"/>
-      <c r="K129" s="17" t="inlineStr"/>
-      <c r="L129" s="17" t="inlineStr"/>
-      <c r="M129" s="17" t="inlineStr"/>
-      <c r="N129" s="18" t="n">
-        <v>48997.375</v>
-      </c>
-      <c r="O129" s="18" t="n">
-        <v>19141.918</v>
-      </c>
-      <c r="P129" s="18" t="n">
-        <v>168.21</v>
+      <c r="B128" s="17" t="inlineStr"/>
+      <c r="C128" s="17" t="inlineStr"/>
+      <c r="D128" s="17" t="inlineStr"/>
+      <c r="E128" s="17" t="inlineStr"/>
+      <c r="F128" s="17" t="inlineStr"/>
+      <c r="G128" s="17" t="inlineStr"/>
+      <c r="H128" s="17" t="inlineStr"/>
+      <c r="I128" s="17" t="inlineStr"/>
+      <c r="J128" s="17" t="inlineStr"/>
+      <c r="K128" s="17" t="inlineStr"/>
+      <c r="L128" s="17" t="inlineStr"/>
+      <c r="M128" s="17" t="inlineStr"/>
+      <c r="N128" s="18" t="n">
+        <v>48290.375</v>
+      </c>
+      <c r="O128" s="18" t="n">
+        <v>23173.468</v>
+      </c>
+      <c r="P128" s="18" t="n">
+        <v>203.19</v>
       </c>
     </row>
   </sheetData>
@@ -9889,7 +9817,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10731,7 +10658,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>22.25</v>
+        <v>22.5</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -10740,7 +10667,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>24.75</v>
+        <v>25</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>5.5</v>
@@ -10750,7 +10677,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10689,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>58</v>
+        <v>58.5</v>
       </c>
     </row>
   </sheetData>
@@ -10847,16 +10774,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>393560</v>
+        <v>389529</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>167963</v>
+        <v>165331</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>225598</v>
+        <v>224198</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>140608</v>
+        <v>139208</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>18223</v>
@@ -10872,10 +10799,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>163911</v>
+        <v>163583</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>62267</v>
+        <v>61939</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>101644</v>
@@ -10897,16 +10824,16 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>229649</v>
+        <v>225946</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>105695</v>
+        <v>103392</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>123954</v>
+        <v>122554</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>53849</v>
+        <v>52449</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>9048</v>

--- a/jira_export_2026-09-14.xlsx
+++ b/jira_export_2026-09-14.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>195 h</t>
+          <t>200 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P128"/>
+  <dimension ref="A1:P129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1054,32 +1054,32 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35518</t>
+          <t>PDMDEP-35572</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PRIVAS] - Migration Placier sans nouveau matériel</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)] - Réinstallation nouveaux serveurs (test et prod)</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE PRIVAS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Migration Placier sans nouveau matériel</t>
+          <t>Réinstallation nouveaux serveurs (test et prod)</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
@@ -1089,26 +1089,30 @@
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35532</t>
-        </is>
-      </c>
-      <c r="M5" s="11" t="inlineStr"/>
+          <t>PDMDEP-35576</t>
+        </is>
+      </c>
+      <c r="M5" s="11" t="inlineStr">
+        <is>
+          <t>00180891</t>
+        </is>
+      </c>
       <c r="N5" s="12" t="n">
         <v>0</v>
       </c>
@@ -1122,32 +1126,32 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35435</t>
+          <t>PDMDEP-35518</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>[CD 92] - Modélisation suite audit sur site</t>
+          <t>[COMMUNE DE PRIVAS] - Migration Placier sans nouveau matériel</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+          <t>COMMUNE DE PRIVAS</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Modélisation suite audit sur site</t>
+          <t>Migration Placier sans nouveau matériel</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -1157,69 +1161,65 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="J6" s="14" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>2.75</v>
+        <v>0.5</v>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35439</t>
-        </is>
-      </c>
-      <c r="M6" s="14" t="inlineStr">
-        <is>
-          <t>00180506</t>
-        </is>
-      </c>
+          <t>PDMDEP-35532</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr"/>
       <c r="N6" s="15" t="n">
-        <v>1470.38</v>
-      </c>
-      <c r="O6" s="16" t="n">
-        <v>1033.24</v>
+        <v>0</v>
+      </c>
+      <c r="O6" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P6" s="15" t="n">
-        <v>375.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35401</t>
+          <t>PDMDEP-35435</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Saint Cast le Guildo ] - Migration GEODP 2 </t>
+          <t>[CD 92] - Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP 2 </t>
+          <t>Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -1229,49 +1229,49 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="J7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.75</v>
+        <v>2.75</v>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35410</t>
+          <t>PDMDEP-35439</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>00173074</t>
+          <t>00180506</t>
         </is>
       </c>
       <c r="N7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="12" t="n">
-        <v>0</v>
+        <v>1470.38</v>
+      </c>
+      <c r="O7" s="16" t="n">
+        <v>1033.24</v>
       </c>
       <c r="P7" s="12" t="n">
-        <v>0</v>
+        <v>375.72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35313</t>
+          <t>PDMDEP-35401</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAREOULT] - Migration Geodp Placier</t>
+          <t xml:space="preserve">[Commune de Saint Cast le Guildo ] - Migration GEODP 2 </t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -1281,12 +1281,12 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAREOULT</t>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Migration Geodp Placier</t>
+          <t xml:space="preserve">Migration GEODP 2 </t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -1306,23 +1306,23 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="J8" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35319</t>
+          <t>PDMDEP-35410</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>00179389</t>
+          <t>00173074</t>
         </is>
       </c>
       <c r="N8" s="15" t="n">
@@ -1338,32 +1338,32 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35184</t>
+          <t>PDMDEP-35313</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAILLARD] - Prestation forfait - Reprise de charte graphique</t>
+          <t>[COMMUNE DE GAREOULT] - Migration Geodp Placier</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Marine MASINGARBE</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE DE GAREOULT</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Prestation forfait - Reprise de charte graphique</t>
+          <t>Migration Geodp Placier</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -1373,69 +1373,69 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35188</t>
+          <t>PDMDEP-35319</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>00178947</t>
+          <t>00179389</t>
         </is>
       </c>
       <c r="N9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>902.72</v>
+        <v>0</v>
       </c>
       <c r="P9" s="12" t="n">
-        <v>451.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35148</t>
+          <t>PDMDEP-35184</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DES PORTES EN RE] - UPSELL PAX</t>
+          <t>[COMMUNE DE GAILLARD] - Prestation forfait - Reprise de charte graphique</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Marine MASINGARBE</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Les Portes En Ré</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PAX</t>
+          <t>Prestation forfait - Reprise de charte graphique</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -1450,44 +1450,44 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="J10" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35156</t>
+          <t>PDMDEP-35188</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>00178841</t>
+          <t>00178947</t>
         </is>
       </c>
       <c r="N10" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>250</v>
+        <v>902.72</v>
       </c>
       <c r="P10" s="15" t="n">
-        <v>0</v>
+        <v>451.36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35105</t>
+          <t>PDMDEP-35148</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
+          <t>[MAIRIE DES PORTES EN RE] - UPSELL PAX</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CARNAC</t>
+          <t>Mairie de Les Portes En Ré</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>UPSELL PAX</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
@@ -1533,19 +1533,19 @@
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35114</t>
+          <t>PDMDEP-35156</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00178806</t>
+          <t>00178841</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>98.5</v>
+        <v>250</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
@@ -1554,42 +1554,42 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35037</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
+          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
@@ -1601,15 +1601,23 @@
         <v>1</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L12" s="14" t="inlineStr"/>
-      <c r="M12" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35114</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="inlineStr">
+        <is>
+          <t>00178806</t>
+        </is>
+      </c>
       <c r="N12" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="P12" s="15" t="n">
         <v>0</v>
@@ -1618,12 +1626,12 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35029</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE LEVALLOIS PERRET] - Hébergement Litt Exp test et prod</t>
+          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1633,12 +1641,12 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE LEVALLOIS PERRET</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hébergement Litt Exp </t>
+          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1648,7 +1656,7 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -1665,7 +1673,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>7.5</v>
+        <v>1.75</v>
       </c>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="11" t="inlineStr"/>
@@ -1682,27 +1690,27 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35029</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>[VILLE DE LEVALLOIS PERRET] - Hébergement Litt Exp test et prod</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>VILLE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t xml:space="preserve">Hébergement Litt Exp </t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -1712,7 +1720,7 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
@@ -1722,29 +1730,21 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34979</t>
-        </is>
-      </c>
-      <c r="M14" s="14" t="inlineStr">
-        <is>
-          <t>00178226</t>
-        </is>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="L14" s="14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
       <c r="N14" s="15" t="n">
-        <v>1100</v>
-      </c>
-      <c r="O14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="15" t="n">
@@ -1754,32 +1754,32 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34819</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Ville de Bourges</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34825</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00177218</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>2419</v>
+        <v>1100</v>
       </c>
       <c r="O15" s="16" t="n">
-        <v>120.95</v>
+        <v>0</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
@@ -1826,27 +1826,27 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
@@ -1873,52 +1873,52 @@
         <v>2</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="15" t="n">
-        <v>643.95</v>
+        <v>2419</v>
+      </c>
+      <c r="O16" s="16" t="n">
+        <v>120.95</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>321.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34761</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1933,69 +1933,69 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34768</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00177029</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>1507.95</v>
+        <v>643.95</v>
       </c>
       <c r="P17" s="12" t="n">
-        <v>0</v>
+        <v>321.98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34761</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Crédits d'heure (14h)</t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -2005,49 +2005,49 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34768</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00177029</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>1260</v>
-      </c>
-      <c r="O18" s="16" t="n">
-        <v>784</v>
+        <v>0</v>
+      </c>
+      <c r="O18" s="15" t="n">
+        <v>1507.95</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>268.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2082,64 +2082,64 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>1.25</v>
+        <v>2.92</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="12" t="n">
-        <v>0</v>
+        <v>1260</v>
+      </c>
+      <c r="O19" s="16" t="n">
+        <v>784</v>
       </c>
       <c r="P19" s="12" t="n">
-        <v>0</v>
+        <v>268.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34631</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>acquisition geodp caisse</t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
@@ -2161,23 +2161,23 @@
         <v>2</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34640</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00176477</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="P20" s="15" t="n">
         <v>0</v>
@@ -2186,12 +2186,12 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34580</t>
+          <t>PDMDEP-34631</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
+          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RIEZ</t>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER simple</t>
+          <t>acquisition geodp caisse</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
@@ -2237,19 +2237,19 @@
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34589</t>
+          <t>PDMDEP-34640</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00176128</t>
+          <t>00176477</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
@@ -2258,32 +2258,32 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>COMMUNE DE RIEZ</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t>MIGRATION GEODP PLACIER simple</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -2293,69 +2293,69 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34589</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176128</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="P22" s="15" t="n">
-        <v>49.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34475</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[Mairie de Pontcharra] - Migration simple placier</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Pontcharra</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Migration simple placier</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2365,49 +2365,49 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34481</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00172611</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="P23" s="12" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Mairie de Pontcharra] - Migration simple placier</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration simple placier</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2442,44 +2442,44 @@
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J24" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="P24" s="15" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2514,29 +2514,29 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P25" s="12" t="n">
@@ -2546,27 +2546,27 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
@@ -2586,21 +2586,29 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L26" s="14" t="inlineStr"/>
-      <c r="M26" s="14" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L26" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34326</t>
+        </is>
+      </c>
+      <c r="M26" s="14" t="inlineStr">
+        <is>
+          <t>00171691</t>
+        </is>
+      </c>
       <c r="N26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="15" t="n">
+        <v>769.5</v>
+      </c>
+      <c r="O26" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="15" t="n">
@@ -2610,27 +2618,27 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2640,7 +2648,7 @@
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -2657,22 +2665,14 @@
         <v>3</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34258</t>
-        </is>
-      </c>
-      <c r="M27" s="11" t="inlineStr">
-        <is>
-          <t>00171361</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L27" s="11" t="inlineStr"/>
+      <c r="M27" s="11" t="inlineStr"/>
       <c r="N27" s="12" t="n">
-        <v>2127.2</v>
-      </c>
-      <c r="O27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="12" t="n">
@@ -2682,32 +2682,32 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2717,69 +2717,69 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O28" s="16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="P28" s="15" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2789,49 +2789,49 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O29" s="16" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="P29" s="12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
@@ -2873,52 +2873,52 @@
         <v>3</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O30" s="16" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="P30" s="15" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2933,69 +2933,69 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O31" s="16" t="n">
-        <v>3849.24</v>
+        <v>277</v>
       </c>
       <c r="P31" s="12" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34126</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[SETE] - AME LiEx</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>AME LiEx</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -3005,35 +3005,35 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34130</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00170928</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="15" t="n">
-        <v>0</v>
+        <v>9623.1</v>
+      </c>
+      <c r="O32" s="16" t="n">
+        <v>3849.24</v>
       </c>
       <c r="P32" s="15" t="n">
         <v>0</v>
@@ -3042,32 +3042,32 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34126</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t>[SETE] - AME LiEx</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>AME LiEx</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3077,35 +3077,35 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34130</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>00170928</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>177.5</v>
+        <v>0</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
@@ -3114,27 +3114,27 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
@@ -3165,19 +3165,19 @@
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="O34" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O34" s="15" t="n">
+        <v>177.5</v>
       </c>
       <c r="P34" s="15" t="n">
         <v>0</v>
@@ -3186,27 +3186,27 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3221,69 +3221,69 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O35" s="16" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="P35" s="12" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3293,64 +3293,64 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>242.9</v>
-      </c>
-      <c r="O36" s="15" t="n">
-        <v>1242.9</v>
+        <v>510</v>
+      </c>
+      <c r="O36" s="16" t="n">
+        <v>51</v>
       </c>
       <c r="P36" s="15" t="n">
-        <v>621.45</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3377,37 +3377,37 @@
         <v>3</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>220</v>
-      </c>
-      <c r="O37" s="16" t="n">
-        <v>0</v>
+        <v>242.9</v>
+      </c>
+      <c r="O37" s="12" t="n">
+        <v>1242.9</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>0</v>
+        <v>621.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -3442,44 +3442,44 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="15" t="n">
-        <v>65.73</v>
+        <v>220</v>
+      </c>
+      <c r="O38" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P38" s="15" t="n">
-        <v>43.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3521,52 +3521,52 @@
         <v>3</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O39" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O39" s="12" t="n">
+        <v>65.73</v>
       </c>
       <c r="P39" s="12" t="n">
-        <v>0</v>
+        <v>32.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
@@ -3586,44 +3586,44 @@
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="15" t="n">
-        <v>465.85</v>
+        <v>1890</v>
+      </c>
+      <c r="O40" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P40" s="15" t="n">
-        <v>93.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3658,59 +3658,59 @@
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>920</v>
-      </c>
-      <c r="O41" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O41" s="12" t="n">
+        <v>465.85</v>
       </c>
       <c r="P41" s="12" t="n">
-        <v>0</v>
+        <v>93.17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3737,37 +3737,37 @@
         <v>3</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="15" t="n">
-        <v>679.5</v>
+        <v>920</v>
+      </c>
+      <c r="O42" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P42" s="15" t="n">
-        <v>906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3813,53 +3813,53 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>540</v>
+        <v>679.5</v>
       </c>
       <c r="P43" s="12" t="n">
-        <v>720</v>
+        <v>906</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3869,64 +3869,64 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>505</v>
+        <v>540</v>
       </c>
       <c r="P44" s="15" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
@@ -3953,23 +3953,23 @@
         <v>3</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
@@ -3978,12 +3978,12 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4013,69 +4013,69 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>691.9</v>
+        <v>0</v>
       </c>
       <c r="P46" s="15" t="n">
-        <v>461.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4085,69 +4085,69 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O47" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O47" s="12" t="n">
+        <v>691.9</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>0</v>
+        <v>461.27</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
@@ -4173,19 +4173,19 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="15" t="n">
-        <v>3339.2</v>
+        <v>171.4</v>
+      </c>
+      <c r="O48" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P48" s="15" t="n">
         <v>0</v>
@@ -4194,27 +4194,27 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4245,19 +4245,19 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>344</v>
-      </c>
-      <c r="O49" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O49" s="12" t="n">
+        <v>3339.2</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>0</v>
@@ -4266,27 +4266,27 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
@@ -4317,16 +4317,16 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4338,27 +4338,27 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
@@ -4389,16 +4389,16 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4410,32 +4410,32 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4445,38 +4445,38 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O52" s="16" t="n">
-        <v>337.5</v>
+        <v>0</v>
       </c>
       <c r="P52" s="15" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4533,53 +4533,53 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="12" t="n">
-        <v>16</v>
+        <v>625</v>
+      </c>
+      <c r="O53" s="16" t="n">
+        <v>337.5</v>
       </c>
       <c r="P53" s="12" t="n">
-        <v>25.6</v>
+        <v>540</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4589,49 +4589,49 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>910</v>
-      </c>
-      <c r="O54" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O54" s="15" t="n">
+        <v>16</v>
       </c>
       <c r="P54" s="15" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4666,27 +4666,27 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4698,32 +4698,32 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4733,32 +4733,32 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4770,32 +4770,32 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
@@ -4817,57 +4817,57 @@
         <v>5</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="12" t="n">
-        <v>1400</v>
+        <v>500</v>
+      </c>
+      <c r="O57" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P57" s="12" t="n">
-        <v>466.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4877,49 +4877,49 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="P58" s="15" t="n">
-        <v>0</v>
+        <v>466.67</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -4929,12 +4929,12 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4954,29 +4954,29 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
@@ -4986,32 +4986,32 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5021,32 +5021,32 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K60" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5058,32 +5058,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5093,34 +5093,34 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="12" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O61" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -5130,32 +5130,32 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -5165,28 +5165,28 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
@@ -5202,12 +5202,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5242,29 +5242,29 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
@@ -5274,32 +5274,32 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -5309,69 +5309,69 @@
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O64" s="16" t="n">
-        <v>136.5</v>
+        <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
-        <v>68.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5381,49 +5381,49 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>590.15</v>
+        <v>910</v>
       </c>
       <c r="O65" s="16" t="n">
-        <v>0</v>
+        <v>136.5</v>
       </c>
       <c r="P65" s="12" t="n">
-        <v>0</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
@@ -5469,19 +5469,19 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="15" t="n">
-        <v>823.65</v>
+        <v>590.15</v>
+      </c>
+      <c r="O66" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P66" s="15" t="n">
         <v>0</v>
@@ -5490,12 +5490,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
@@ -5541,19 +5541,19 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="O67" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O67" s="12" t="n">
+        <v>823.65</v>
       </c>
       <c r="P67" s="12" t="n">
         <v>0</v>
@@ -5562,32 +5562,32 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -5602,27 +5602,27 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5634,12 +5634,12 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5674,27 +5674,27 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5706,32 +5706,32 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
@@ -5757,16 +5757,16 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5778,12 +5778,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5818,59 +5818,59 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="12" t="n">
-        <v>1470</v>
+        <v>588</v>
+      </c>
+      <c r="O71" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
-        <v>452.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5885,49 +5885,49 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O72" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O72" s="15" t="n">
+        <v>1470</v>
       </c>
       <c r="P72" s="15" t="n">
-        <v>0</v>
+        <v>452.31</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5957,12 +5957,12 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
@@ -5973,16 +5973,16 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O73" s="16" t="n">
         <v>0</v>
@@ -5994,32 +5994,32 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
@@ -6045,16 +6045,16 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6066,27 +6066,27 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -6106,29 +6106,29 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="12" t="n">
+        <v>700</v>
+      </c>
+      <c r="O75" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
@@ -6138,32 +6138,32 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6173,34 +6173,34 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>210</v>
-      </c>
-      <c r="O76" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="15" t="n">
@@ -6210,12 +6210,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6261,19 +6261,19 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="12" t="n">
-        <v>281</v>
+        <v>210</v>
+      </c>
+      <c r="O77" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P77" s="12" t="n">
         <v>0</v>
@@ -6282,12 +6282,12 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
@@ -6333,19 +6333,19 @@
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="O78" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O78" s="15" t="n">
+        <v>281</v>
       </c>
       <c r="P78" s="15" t="n">
         <v>0</v>
@@ -6354,12 +6354,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
@@ -6405,16 +6405,16 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O79" s="16" t="n">
         <v>0</v>
@@ -6426,12 +6426,12 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -6466,27 +6466,27 @@
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K80" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O80" s="16" t="n">
         <v>0</v>
@@ -6498,32 +6498,32 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -6533,32 +6533,32 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O81" s="16" t="n">
         <v>0</v>
@@ -6570,27 +6570,27 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
@@ -6610,29 +6610,29 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="15" t="n">
+        <v>690</v>
+      </c>
+      <c r="O82" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="15" t="n">
@@ -6693,18 +6693,18 @@
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O83" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -6765,16 +6765,16 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O84" s="16" t="n">
         <v>0</v>
@@ -6786,32 +6786,32 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6821,35 +6821,35 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="12" t="n">
-        <v>362.5</v>
+        <v>787.5</v>
+      </c>
+      <c r="O85" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
         <v>0</v>
@@ -6858,30 +6858,32 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E86" s="14" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -6891,35 +6893,35 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P86" s="15" t="n">
         <v>0</v>
@@ -6928,12 +6930,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6943,13 +6945,11 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E87" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v/>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
@@ -6968,23 +6968,23 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0.95</v>
+        <v>2.75</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
@@ -7267,18 +7267,18 @@
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O91" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="12" t="n">
@@ -7288,12 +7288,12 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
@@ -7303,11 +7303,13 @@
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E92" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
@@ -7321,34 +7323,34 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O92" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7358,12 +7360,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7373,34 +7375,48 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F93" s="11" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H93" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" s="11" t="inlineStr"/>
-      <c r="M93" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L93" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27642</t>
+        </is>
+      </c>
+      <c r="M93" s="11" t="inlineStr">
+        <is>
+          <t>00143935</t>
+        </is>
+      </c>
       <c r="N93" s="12" t="n">
         <v>0</v>
       </c>
@@ -7414,12 +7430,12 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
@@ -7429,48 +7445,34 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="n">
-        <v/>
-      </c>
-      <c r="F94" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F94" s="14" t="inlineStr"/>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H94" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H94" s="14" t="inlineStr"/>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L94" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M94" s="14" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L94" s="14" t="inlineStr"/>
+      <c r="M94" s="14" t="inlineStr"/>
       <c r="N94" s="15" t="n">
         <v>0</v>
       </c>
@@ -7484,12 +7486,12 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
@@ -7499,7 +7501,7 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7517,34 +7519,34 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O95" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="12" t="n">
@@ -7554,12 +7556,12 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
@@ -7569,7 +7571,7 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7592,44 +7594,44 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="15" t="n">
-        <v>416.188</v>
+        <v>1212</v>
+      </c>
+      <c r="O96" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P96" s="15" t="n">
-        <v>277.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7639,13 +7641,11 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v/>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
@@ -7654,54 +7654,54 @@
       </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>13</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O97" s="12" t="n">
-        <v>0</v>
+        <v>416.188</v>
       </c>
       <c r="P97" s="12" t="n">
-        <v>0</v>
+        <v>277.46</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
@@ -7711,11 +7711,13 @@
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
-        </is>
-      </c>
-      <c r="E98" s="14" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -7724,33 +7726,33 @@
       </c>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
@@ -7766,12 +7768,12 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7781,7 +7783,7 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7804,23 +7806,23 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
         <v>14</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0.06</v>
+        <v>1.5</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
@@ -7885,12 +7887,12 @@
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
@@ -7921,7 +7923,7 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7955,12 +7957,12 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
@@ -7991,7 +7993,7 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -8025,12 +8027,12 @@
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
@@ -8046,12 +8048,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22126</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8061,7 +8063,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Métropole Européenne de Lille</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8079,28 +8081,28 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27368</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>484163</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
@@ -8116,22 +8118,22 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22126</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>Métropole Européenne de Lille</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8154,29 +8156,29 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27368</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>484163</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O104" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="15" t="n">
@@ -8186,12 +8188,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8201,7 +8203,7 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8219,34 +8221,34 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O105" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8256,22 +8258,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8289,28 +8291,28 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
@@ -8326,22 +8328,22 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8364,29 +8366,29 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O107" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8396,12 +8398,12 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -8411,7 +8413,7 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
@@ -8434,29 +8436,29 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O108" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="15" t="n">
@@ -8466,22 +8468,22 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8499,28 +8501,28 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K109" s="11" t="n">
         <v>0.5</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
@@ -8585,12 +8587,12 @@
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
@@ -8606,12 +8608,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8621,7 +8623,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8634,27 +8636,35 @@
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L111" s="11" t="inlineStr"/>
-      <c r="M111" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N111" s="12" t="n">
         <v>0</v>
       </c>
@@ -8668,22 +8678,22 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8701,7 +8711,7 @@
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
@@ -8713,7 +8723,7 @@
         <v>21</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>5.58</v>
+        <v>5.5</v>
       </c>
       <c r="L112" s="14" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -8730,22 +8740,22 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8753,44 +8763,36 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
         <v>21</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M113" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>5.58</v>
+      </c>
+      <c r="L113" s="11" t="inlineStr"/>
+      <c r="M113" s="11" t="inlineStr"/>
       <c r="N113" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O113" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
@@ -8800,22 +8802,22 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
@@ -8823,7 +8825,7 @@
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G114" s="14" t="inlineStr">
@@ -8833,34 +8835,34 @@
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
         <v>21</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O114" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="15" t="n">
@@ -8885,7 +8887,7 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8919,7 +8921,7 @@
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
@@ -8940,12 +8942,12 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -8955,7 +8957,7 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -8985,22 +8987,22 @@
         <v>21</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O116" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="15" t="n">
@@ -9010,22 +9012,22 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9038,7 +9040,7 @@
       </c>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr">
@@ -9048,21 +9050,29 @@
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L117" s="11" t="inlineStr"/>
-      <c r="M117" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L117" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M117" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O117" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="12" t="n">
@@ -9072,12 +9082,12 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
@@ -9087,7 +9097,7 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9105,19 +9115,19 @@
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>3.58</v>
+        <v>0.5</v>
       </c>
       <c r="L118" s="14" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -9134,22 +9144,22 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9162,35 +9172,27 @@
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L119" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M119" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>3.58</v>
+      </c>
+      <c r="L119" s="11" t="inlineStr"/>
+      <c r="M119" s="11" t="inlineStr"/>
       <c r="N119" s="12" t="n">
         <v>0</v>
       </c>
@@ -9204,22 +9206,22 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9232,23 +9234,35 @@
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H120" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H120" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L120" s="14" t="inlineStr"/>
-      <c r="M120" s="14" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L120" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M120" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N120" s="15" t="n">
         <v>0</v>
       </c>
@@ -9262,28 +9276,26 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E121" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v/>
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
@@ -9295,21 +9307,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H121" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H121" s="11" t="inlineStr"/>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L121" s="11" t="inlineStr"/>
       <c r="M121" s="11" t="inlineStr"/>
@@ -9326,23 +9334,27 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C122" s="14" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F122" s="14" t="inlineStr">
@@ -9357,19 +9369,19 @@
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>2.75</v>
+        <v>0.25</v>
       </c>
       <c r="L122" s="14" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -9386,21 +9398,25 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr"/>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E123" s="11" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9408,26 +9424,26 @@
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H123" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L123" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="L123" s="11" t="inlineStr"/>
       <c r="M123" s="11" t="inlineStr"/>
       <c r="N123" s="12" t="n">
         <v>0</v>
@@ -9442,18 +9458,18 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PSC-1334</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr"/>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E124" s="14" t="inlineStr"/>
@@ -9464,7 +9480,7 @@
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H124" s="14" t="inlineStr"/>
@@ -9477,9 +9493,13 @@
         <v>2</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L124" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L124" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
       <c r="M124" s="14" t="inlineStr"/>
       <c r="N124" s="15" t="n">
         <v>0</v>
@@ -9494,18 +9514,18 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1334</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr"/>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr"/>
@@ -9516,31 +9536,23 @@
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr"/>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L125" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M125" s="11" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L125" s="11" t="inlineStr"/>
+      <c r="M125" s="11" t="inlineStr"/>
       <c r="N125" s="12" t="n">
         <v>0</v>
       </c>
@@ -9554,18 +9566,18 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr"/>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E126" s="14" t="inlineStr"/>
@@ -9582,23 +9594,23 @@
       <c r="H126" s="14" t="inlineStr"/>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34778</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00172868</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
@@ -9614,18 +9626,18 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PSC-668</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr"/>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr"/>
@@ -9636,59 +9648,119 @@
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr"/>
       <c r="I127" s="11" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J127" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K127" s="11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L127" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N127" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="13" t="inlineStr">
+        <is>
+          <t>PSC-668</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="C128" s="14" t="inlineStr"/>
+      <c r="D128" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="E128" s="14" t="inlineStr"/>
+      <c r="F128" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G128" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H128" s="14" t="inlineStr"/>
+      <c r="I128" s="14" t="inlineStr">
+        <is>
           <t>04/04/2025</t>
         </is>
       </c>
-      <c r="J127" s="11" t="n">
+      <c r="J128" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="K127" s="11" t="n">
+      <c r="K128" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L127" s="11" t="inlineStr"/>
-      <c r="M127" s="11" t="inlineStr"/>
-      <c r="N127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="17" t="inlineStr">
+      <c r="L128" s="14" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+      <c r="N128" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B128" s="17" t="inlineStr"/>
-      <c r="C128" s="17" t="inlineStr"/>
-      <c r="D128" s="17" t="inlineStr"/>
-      <c r="E128" s="17" t="inlineStr"/>
-      <c r="F128" s="17" t="inlineStr"/>
-      <c r="G128" s="17" t="inlineStr"/>
-      <c r="H128" s="17" t="inlineStr"/>
-      <c r="I128" s="17" t="inlineStr"/>
-      <c r="J128" s="17" t="inlineStr"/>
-      <c r="K128" s="17" t="inlineStr"/>
-      <c r="L128" s="17" t="inlineStr"/>
-      <c r="M128" s="17" t="inlineStr"/>
-      <c r="N128" s="18" t="n">
+      <c r="B129" s="17" t="inlineStr"/>
+      <c r="C129" s="17" t="inlineStr"/>
+      <c r="D129" s="17" t="inlineStr"/>
+      <c r="E129" s="17" t="inlineStr"/>
+      <c r="F129" s="17" t="inlineStr"/>
+      <c r="G129" s="17" t="inlineStr"/>
+      <c r="H129" s="17" t="inlineStr"/>
+      <c r="I129" s="17" t="inlineStr"/>
+      <c r="J129" s="17" t="inlineStr"/>
+      <c r="K129" s="17" t="inlineStr"/>
+      <c r="L129" s="17" t="inlineStr"/>
+      <c r="M129" s="17" t="inlineStr"/>
+      <c r="N129" s="18" t="n">
         <v>48290.375</v>
       </c>
-      <c r="O128" s="18" t="n">
+      <c r="O129" s="18" t="n">
         <v>23173.468</v>
       </c>
-      <c r="P128" s="18" t="n">
-        <v>203.19</v>
+      <c r="P129" s="18" t="n">
+        <v>199.69</v>
       </c>
     </row>
   </sheetData>
@@ -9817,6 +9889,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10628,7 +10701,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>58.92</v>
+        <v>60.92</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>19.17</v>
@@ -10637,17 +10710,17 @@
         <v>10</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>88.08</v>
+        <v>90.08</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>15.42</v>
+        <v>17.17</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>652.05</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -10689,7 +10762,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>58.5</v>
+        <v>59.25</v>
       </c>
     </row>
   </sheetData>
@@ -10774,10 +10847,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>389529</v>
+        <v>398994</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>165331</v>
+        <v>174797</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>224198</v>
@@ -10799,10 +10872,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>163583</v>
+        <v>173048</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>61939</v>
+        <v>71404</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>101644</v>
@@ -10853,7 +10926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10877,7 +10950,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 14 commande(s)</t>
+          <t>Épics créées ce mois — 16 commande(s)</t>
         </is>
       </c>
     </row>
@@ -10932,22 +11005,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35636</t>
+          <t>PDMDEP-35672</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35627</t>
+          <t>PDMDEP-35666</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANNEMASSE</t>
+          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -10967,7 +11040,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00181182</t>
+          <t>00181382</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -10977,22 +11050,22 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35606</t>
+          <t>PDMDEP-35636</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35597</t>
+          <t>PDMDEP-35627</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE D'ANNEMASSE</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -11012,7 +11085,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00181049</t>
+          <t>00181182</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
@@ -11022,22 +11095,22 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35587</t>
+          <t>PDMDEP-35606</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35583</t>
+          <t>PDMDEP-35597</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -11047,7 +11120,7 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -11057,7 +11130,7 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00180931</t>
+          <t>00181049</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
@@ -11067,22 +11140,22 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35532</t>
+          <t>PDMDEP-35587</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35518</t>
+          <t>PDMDEP-35583</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE PRIVAS</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -11092,34 +11165,42 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr"/>
-      <c r="H8" s="11" t="inlineStr"/>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>00180931</t>
+        </is>
+      </c>
       <c r="I8" s="26" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35532</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35518</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>COMMUNE DE PRIVAS</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -11132,39 +11213,31 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>00180643</t>
-        </is>
-      </c>
+      <c r="G9" s="14" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr"/>
       <c r="I9" s="25" t="n">
-        <v>6285</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35410</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35401</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -11184,22 +11257,22 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00173074</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>1200</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35410</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35401</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -11209,7 +11282,7 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -11229,42 +11302,42 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00173074</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>28915.01</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35652</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35646</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE GEX</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -11274,32 +11347,32 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00181167</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>0</v>
+        <v>28915.01</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35622</t>
+          <t>PDMDEP-35687</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35618</t>
+          <t>PDMDEP-35683</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Roche-sur-Yon</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -11319,32 +11392,32 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00181123</t>
+          <t>00181396</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>0</v>
+        <v>2333.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35576</t>
+          <t>PDMDEP-35652</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35572</t>
+          <t>PDMDEP-35646</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
+          <t>VILLE DE GEX</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -11364,32 +11437,32 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00180891</t>
+          <t>00181167</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>0</v>
+        <v>6382.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35622</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35618</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>Commune de la Roche-sur-Yon</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -11409,7 +11482,7 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00181123</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
@@ -11419,22 +11492,22 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35511</t>
+          <t>PDMDEP-35576</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35504</t>
+          <t>PDMDEP-35572</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>[TEST]</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -11444,7 +11517,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -11454,32 +11527,32 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>0015489263</t>
+          <t>00180891</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -11499,104 +11572,152 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="I17" s="25" t="n">
-        <v>455</v>
+        <v>895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-35511</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35504</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>[TEST]</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>0015489263</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35464</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35460</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>00180631</t>
+        </is>
+      </c>
+      <c r="I19" s="25" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-35439</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-35435</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>03/09/2026</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>00180506</t>
         </is>
       </c>
-      <c r="I18" s="26" t="n">
+      <c r="I20" s="26" t="n">
         <v>3974</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="17" t="n"/>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>14 commande(s)</t>
-        </is>
-      </c>
-      <c r="I19" s="24" t="n">
-        <v>42279</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>dont Littéralis</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
-      <c r="F20" s="17" t="n"/>
-      <c r="G20" s="17" t="n"/>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>7 commande(s)</t>
-        </is>
-      </c>
-      <c r="I20" s="24" t="n">
-        <v>4429</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B21" s="17" t="n"/>
@@ -11607,10 +11728,52 @@
       <c r="G21" s="17" t="n"/>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>7 commande(s)</t>
+          <t>16 commande(s)</t>
         </is>
       </c>
       <c r="I21" s="24" t="n">
+        <v>52730</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>dont Littéralis</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>8 commande(s)</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="n">
+        <v>14880</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="17" t="n"/>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>8 commande(s)</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="n">
         <v>37850</v>
       </c>
     </row>

--- a/jira_export_2026-09-14.xlsx
+++ b/jira_export_2026-09-14.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>23,173 €</t>
+          <t>23,785 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,14 +760,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>6,864 €</t>
+          <t>6,907 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>16,309 €</t>
+          <t>16,878 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>200 h</t>
+          <t>206 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -916,7 +916,7 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B29" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P129"/>
+  <dimension ref="A1:P132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -2377,7 +2377,7 @@
         <v>2</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
@@ -2393,10 +2393,10 @@
         <v>0</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="P23" s="12" t="n">
-        <v>43</v>
+        <v>45.26</v>
       </c>
     </row>
     <row r="24">
@@ -3521,7 +3521,7 @@
         <v>3</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>65.73</v>
       </c>
       <c r="P39" s="12" t="n">
-        <v>32.87</v>
+        <v>29.21</v>
       </c>
     </row>
     <row r="40">
@@ -3906,12 +3906,12 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33638</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DE MOULINS</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Migration GeODP Placier et MEP module Caisse</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
@@ -3957,19 +3957,19 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33647</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169251</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>505</v>
+        <v>568.8</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
@@ -3978,27 +3978,27 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
@@ -4025,23 +4025,23 @@
         <v>3</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="P46" s="15" t="n">
         <v>0</v>
@@ -4050,12 +4050,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4085,69 +4085,69 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>691.9</v>
+        <v>0</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>461.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -4157,69 +4157,69 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O48" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O48" s="15" t="n">
+        <v>691.9</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>0</v>
+        <v>461.27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4245,19 +4245,19 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="12" t="n">
-        <v>3339.2</v>
+        <v>171.4</v>
+      </c>
+      <c r="O49" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>0</v>
@@ -4266,27 +4266,27 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
@@ -4317,19 +4317,19 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>344</v>
-      </c>
-      <c r="O50" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O50" s="15" t="n">
+        <v>3339.2</v>
       </c>
       <c r="P50" s="15" t="n">
         <v>0</v>
@@ -4338,27 +4338,27 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
@@ -4389,16 +4389,16 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4410,27 +4410,27 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
@@ -4461,16 +4461,16 @@
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4482,32 +4482,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4517,38 +4517,38 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O53" s="16" t="n">
-        <v>337.5</v>
+        <v>0</v>
       </c>
       <c r="P53" s="12" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4605,53 +4605,53 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="15" t="n">
-        <v>16</v>
+        <v>625</v>
+      </c>
+      <c r="O54" s="16" t="n">
+        <v>337.5</v>
       </c>
       <c r="P54" s="15" t="n">
-        <v>25.6</v>
+        <v>540</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4661,49 +4661,49 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>910</v>
-      </c>
-      <c r="O55" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O55" s="12" t="n">
+        <v>16</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4738,27 +4738,27 @@
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4770,32 +4770,32 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4805,32 +4805,32 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4842,32 +4842,32 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
@@ -4889,57 +4889,57 @@
         <v>5</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="15" t="n">
-        <v>1400</v>
+        <v>500</v>
+      </c>
+      <c r="O58" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
-        <v>466.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4949,49 +4949,49 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O59" s="12" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="P59" s="12" t="n">
-        <v>0</v>
+        <v>466.67</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -5026,29 +5026,29 @@
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="15" t="n">
@@ -5058,32 +5058,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5093,32 +5093,32 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K61" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O61" s="16" t="n">
         <v>0</v>
@@ -5130,32 +5130,32 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -5165,34 +5165,34 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="15" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O62" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P62" s="15" t="n">
@@ -5202,32 +5202,32 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5237,28 +5237,28 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
@@ -5274,12 +5274,12 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -5314,29 +5314,29 @@
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="O64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
@@ -5346,32 +5346,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5381,69 +5381,69 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O65" s="16" t="n">
-        <v>136.5</v>
+        <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
-        <v>68.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -5453,49 +5453,49 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>590.15</v>
+        <v>910</v>
       </c>
       <c r="O66" s="16" t="n">
-        <v>0</v>
+        <v>136.5</v>
       </c>
       <c r="P66" s="15" t="n">
-        <v>0</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
@@ -5541,19 +5541,19 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="12" t="n">
-        <v>823.65</v>
+        <v>590.15</v>
+      </c>
+      <c r="O67" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P67" s="12" t="n">
         <v>0</v>
@@ -5562,12 +5562,12 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
@@ -5613,19 +5613,19 @@
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>285</v>
-      </c>
-      <c r="O68" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O68" s="15" t="n">
+        <v>823.65</v>
       </c>
       <c r="P68" s="15" t="n">
         <v>0</v>
@@ -5634,32 +5634,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5674,27 +5674,27 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5706,12 +5706,12 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -5721,12 +5721,12 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5746,27 +5746,27 @@
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5778,32 +5778,32 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -5829,16 +5829,16 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O71" s="16" t="n">
         <v>0</v>
@@ -5850,12 +5850,12 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5890,59 +5890,59 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15" t="n">
-        <v>1470</v>
+        <v>588</v>
+      </c>
+      <c r="O72" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
-        <v>452.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5957,49 +5957,49 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O73" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O73" s="12" t="n">
+        <v>1470</v>
       </c>
       <c r="P73" s="12" t="n">
-        <v>0</v>
+        <v>452.31</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -6009,12 +6009,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
@@ -6045,16 +6045,16 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6066,32 +6066,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
@@ -6117,16 +6117,16 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O75" s="16" t="n">
         <v>0</v>
@@ -6138,27 +6138,27 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
@@ -6178,29 +6178,29 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="O76" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="15" t="n">
@@ -6210,32 +6210,32 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6245,34 +6245,34 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="O77" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P77" s="12" t="n">
@@ -6282,12 +6282,12 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -6333,19 +6333,19 @@
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="15" t="n">
-        <v>281</v>
+        <v>210</v>
+      </c>
+      <c r="O78" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
         <v>0</v>
@@ -6354,12 +6354,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
@@ -6405,19 +6405,19 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>130</v>
-      </c>
-      <c r="O79" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O79" s="12" t="n">
+        <v>281</v>
       </c>
       <c r="P79" s="12" t="n">
         <v>0</v>
@@ -6426,12 +6426,12 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
@@ -6477,16 +6477,16 @@
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O80" s="16" t="n">
         <v>0</v>
@@ -6498,12 +6498,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -6538,27 +6538,27 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K81" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O81" s="16" t="n">
         <v>0</v>
@@ -6570,32 +6570,32 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -6605,32 +6605,32 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O82" s="16" t="n">
         <v>0</v>
@@ -6642,27 +6642,27 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -6682,29 +6682,29 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="12" t="n">
+        <v>690</v>
+      </c>
+      <c r="O83" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -6765,18 +6765,18 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O84" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="15" t="n">
@@ -6837,16 +6837,16 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O85" s="16" t="n">
         <v>0</v>
@@ -6858,32 +6858,32 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -6893,35 +6893,35 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="15" t="n">
-        <v>362.5</v>
+        <v>787.5</v>
+      </c>
+      <c r="O86" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P86" s="15" t="n">
         <v>0</v>
@@ -6930,30 +6930,32 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E87" s="11" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -6963,35 +6965,35 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O87" s="12" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P87" s="12" t="n">
         <v>0</v>
@@ -7000,12 +7002,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
@@ -7015,13 +7017,11 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E88" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="n">
+        <v/>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -7040,23 +7040,23 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0.95</v>
+        <v>2.75</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
@@ -7339,18 +7339,18 @@
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O92" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7360,12 +7360,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7375,11 +7375,13 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
@@ -7393,34 +7395,34 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O93" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
@@ -7430,12 +7432,12 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
@@ -7445,34 +7447,48 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F94" s="14" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H94" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H94" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" s="14" t="inlineStr"/>
-      <c r="M94" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L94" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27642</t>
+        </is>
+      </c>
+      <c r="M94" s="14" t="inlineStr">
+        <is>
+          <t>00143935</t>
+        </is>
+      </c>
       <c r="N94" s="15" t="n">
         <v>0</v>
       </c>
@@ -7486,12 +7502,12 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
@@ -7501,48 +7517,34 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E95" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F95" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="inlineStr"/>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H95" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H95" s="11" t="inlineStr"/>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L95" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M95" s="11" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L95" s="11" t="inlineStr"/>
+      <c r="M95" s="11" t="inlineStr"/>
       <c r="N95" s="12" t="n">
         <v>0</v>
       </c>
@@ -7556,12 +7558,12 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
@@ -7571,7 +7573,7 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7589,34 +7591,34 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O96" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="15" t="n">
@@ -7626,12 +7628,12 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7641,7 +7643,7 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7664,60 +7666,58 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="12" t="n">
-        <v>416.188</v>
+        <v>1212</v>
+      </c>
+      <c r="O97" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P97" s="12" t="n">
-        <v>277.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E98" s="14" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v/>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H98" s="14" t="inlineStr">
@@ -7736,23 +7736,23 @@
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
@@ -7768,12 +7768,12 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7806,44 +7806,44 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K99" s="11" t="n">
         <v>1.5</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O99" s="12" t="n">
-        <v>0</v>
+        <v>416.188</v>
       </c>
       <c r="P99" s="12" t="n">
-        <v>0</v>
+        <v>277.46</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -7853,11 +7853,13 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
-        </is>
-      </c>
-      <c r="E100" s="14" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -7866,33 +7868,33 @@
       </c>
       <c r="G100" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
@@ -7908,12 +7910,12 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
@@ -7923,7 +7925,7 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7946,23 +7948,23 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
         <v>14</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>0.06</v>
+        <v>1.5</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
@@ -7993,7 +7995,7 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -8027,12 +8029,12 @@
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
@@ -8097,12 +8099,12 @@
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
@@ -8118,12 +8120,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22126</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -8133,7 +8135,7 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>Métropole Européenne de Lille</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8151,28 +8153,28 @@
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27368</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>484163</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
@@ -8188,22 +8190,22 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8221,34 +8223,34 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O105" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8258,22 +8260,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-22126</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>Métropole Européenne de Lille</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8291,28 +8293,28 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>4.5</v>
+        <v>0.25</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27368</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>484163</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
@@ -8328,22 +8330,22 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8366,29 +8368,29 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O107" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8398,12 +8400,12 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -8413,7 +8415,7 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
@@ -8431,34 +8433,34 @@
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O108" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="15" t="n">
@@ -8468,22 +8470,22 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8506,23 +8508,23 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
@@ -8538,22 +8540,22 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
@@ -8571,34 +8573,34 @@
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="15" t="n">
@@ -8608,22 +8610,22 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8646,23 +8648,23 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
@@ -8678,22 +8680,22 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8706,7 +8708,7 @@
       </c>
       <c r="G112" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H112" s="14" t="inlineStr">
@@ -8716,17 +8718,25 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L112" s="14" t="inlineStr"/>
-      <c r="M112" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L112" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27568</t>
+        </is>
+      </c>
+      <c r="M112" s="14" t="inlineStr">
+        <is>
+          <t>471958</t>
+        </is>
+      </c>
       <c r="N112" s="15" t="n">
         <v>0</v>
       </c>
@@ -8740,22 +8750,22 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8768,7 +8778,7 @@
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
@@ -8778,17 +8788,25 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="L113" s="11" t="inlineStr"/>
-      <c r="M113" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28215</t>
+        </is>
+      </c>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>458306</t>
+        </is>
+      </c>
       <c r="N113" s="12" t="n">
         <v>0</v>
       </c>
@@ -8802,22 +8820,22 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
@@ -8825,7 +8843,7 @@
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G114" s="14" t="inlineStr">
@@ -8835,34 +8853,34 @@
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28214</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>458286</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O114" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="15" t="n">
@@ -8872,22 +8890,22 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8900,7 +8918,7 @@
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
@@ -8910,25 +8928,17 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
         <v>21</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L115" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34362</t>
-        </is>
-      </c>
-      <c r="M115" s="11" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>5.5</v>
+      </c>
+      <c r="L115" s="11" t="inlineStr"/>
+      <c r="M115" s="11" t="inlineStr"/>
       <c r="N115" s="12" t="n">
         <v>0</v>
       </c>
@@ -8942,12 +8952,12 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -8957,7 +8967,7 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -8970,35 +8980,27 @@
       </c>
       <c r="G116" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
         <v>21</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L116" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28020</t>
-        </is>
-      </c>
-      <c r="M116" s="14" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>5.58</v>
+      </c>
+      <c r="L116" s="14" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
       <c r="N116" s="15" t="n">
         <v>0</v>
       </c>
@@ -9012,22 +9014,22 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9035,7 +9037,7 @@
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr">
@@ -9045,12 +9047,12 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
@@ -9061,16 +9063,16 @@
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O117" s="16" t="n">
         <v>0</v>
@@ -9082,22 +9084,22 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9110,7 +9112,7 @@
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H118" s="14" t="inlineStr">
@@ -9120,17 +9122,25 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L118" s="14" t="inlineStr"/>
-      <c r="M118" s="14" t="inlineStr"/>
+        <v>0.12</v>
+      </c>
+      <c r="L118" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34362</t>
+        </is>
+      </c>
+      <c r="M118" s="14" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N118" s="15" t="n">
         <v>0</v>
       </c>
@@ -9144,22 +9154,22 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9172,27 +9182,35 @@
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="L119" s="11" t="inlineStr"/>
-      <c r="M119" s="11" t="inlineStr"/>
+        <v>0.12</v>
+      </c>
+      <c r="L119" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M119" s="11" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N119" s="12" t="n">
         <v>0</v>
       </c>
@@ -9206,12 +9224,12 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
@@ -9221,7 +9239,7 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9244,29 +9262,29 @@
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O120" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="15" t="n">
@@ -9276,12 +9294,12 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -9291,7 +9309,7 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9307,17 +9325,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H121" s="11" t="inlineStr"/>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L121" s="11" t="inlineStr"/>
       <c r="M121" s="11" t="inlineStr"/>
@@ -9334,28 +9356,26 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E122" s="14" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>Valenciennes</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="n">
+        <v/>
       </c>
       <c r="F122" s="14" t="inlineStr">
         <is>
@@ -9369,19 +9389,19 @@
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>0.25</v>
+        <v>3.58</v>
       </c>
       <c r="L122" s="14" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -9398,24 +9418,26 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C123" s="11" t="inlineStr"/>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E123" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v/>
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
@@ -9424,27 +9446,35 @@
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L123" s="11" t="inlineStr"/>
-      <c r="M123" s="11" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L123" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M123" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N123" s="12" t="n">
         <v>0</v>
       </c>
@@ -9458,21 +9488,27 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="C124" s="14" t="inlineStr"/>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E124" s="14" t="inlineStr"/>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="n">
+        <v/>
+      </c>
       <c r="F124" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9480,26 +9516,22 @@
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H124" s="14" t="inlineStr"/>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L124" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L124" s="14" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
       <c r="N124" s="15" t="n">
         <v>0</v>
@@ -9514,21 +9546,29 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PSC-1334</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
-        </is>
-      </c>
-      <c r="C125" s="11" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
-        </is>
-      </c>
-      <c r="E125" s="11" t="inlineStr"/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9536,20 +9576,24 @@
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H125" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L125" s="11" t="inlineStr"/>
       <c r="M125" s="11" t="inlineStr"/>
@@ -9566,21 +9610,25 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr"/>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
-        </is>
-      </c>
-      <c r="E126" s="14" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F126" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9588,31 +9636,27 @@
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H126" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H126" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L126" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M126" s="14" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="L126" s="14" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
       <c r="N126" s="15" t="n">
         <v>0</v>
       </c>
@@ -9626,18 +9670,18 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr"/>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr"/>
@@ -9654,25 +9698,21 @@
       <c r="H127" s="11" t="inlineStr"/>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M127" s="11" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr"/>
       <c r="N127" s="12" t="n">
         <v>0</v>
       </c>
@@ -9686,18 +9726,18 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PSC-668</t>
+          <t>PSC-1334</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr"/>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="E128" s="14" t="inlineStr"/>
@@ -9714,14 +9754,14 @@
       <c r="H128" s="14" t="inlineStr"/>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L128" s="14" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -9736,31 +9776,203 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="17" t="inlineStr">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1315</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE RANG DU FLIERS</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr"/>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE RANG DU FLIERS</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr"/>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr"/>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="J129" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K129" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L129" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M129" s="11" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
+      <c r="N129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B130" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C130" s="14" t="inlineStr"/>
+      <c r="D130" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E130" s="14" t="inlineStr"/>
+      <c r="F130" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G130" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H130" s="14" t="inlineStr"/>
+      <c r="I130" s="14" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J130" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K130" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L130" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M130" s="14" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N130" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>PSC-668</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr"/>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr"/>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H131" s="11" t="inlineStr"/>
+      <c r="I131" s="11" t="inlineStr">
+        <is>
+          <t>04/04/2025</t>
+        </is>
+      </c>
+      <c r="J131" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="K131" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L131" s="11" t="inlineStr"/>
+      <c r="M131" s="11" t="inlineStr"/>
+      <c r="N131" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B129" s="17" t="inlineStr"/>
-      <c r="C129" s="17" t="inlineStr"/>
-      <c r="D129" s="17" t="inlineStr"/>
-      <c r="E129" s="17" t="inlineStr"/>
-      <c r="F129" s="17" t="inlineStr"/>
-      <c r="G129" s="17" t="inlineStr"/>
-      <c r="H129" s="17" t="inlineStr"/>
-      <c r="I129" s="17" t="inlineStr"/>
-      <c r="J129" s="17" t="inlineStr"/>
-      <c r="K129" s="17" t="inlineStr"/>
-      <c r="L129" s="17" t="inlineStr"/>
-      <c r="M129" s="17" t="inlineStr"/>
-      <c r="N129" s="18" t="n">
+      <c r="B132" s="17" t="inlineStr"/>
+      <c r="C132" s="17" t="inlineStr"/>
+      <c r="D132" s="17" t="inlineStr"/>
+      <c r="E132" s="17" t="inlineStr"/>
+      <c r="F132" s="17" t="inlineStr"/>
+      <c r="G132" s="17" t="inlineStr"/>
+      <c r="H132" s="17" t="inlineStr"/>
+      <c r="I132" s="17" t="inlineStr"/>
+      <c r="J132" s="17" t="inlineStr"/>
+      <c r="K132" s="17" t="inlineStr"/>
+      <c r="L132" s="17" t="inlineStr"/>
+      <c r="M132" s="17" t="inlineStr"/>
+      <c r="N132" s="18" t="n">
         <v>48290.375</v>
       </c>
-      <c r="O129" s="18" t="n">
-        <v>23173.468</v>
-      </c>
-      <c r="P129" s="18" t="n">
-        <v>199.69</v>
+      <c r="O132" s="18" t="n">
+        <v>23785.268</v>
+      </c>
+      <c r="P132" s="18" t="n">
+        <v>201.06</v>
       </c>
     </row>
   </sheetData>
@@ -9890,6 +10102,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10701,7 +10916,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>60.92</v>
+        <v>63.17</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>19.17</v>
@@ -10710,17 +10925,17 @@
         <v>10</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>90.08</v>
+        <v>92.33</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>17.17</v>
+        <v>17.92</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>652.05</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10977,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>59.25</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -10847,16 +11062,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>398994</v>
+        <v>398383</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>174797</v>
+        <v>174754</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>224198</v>
+        <v>223629</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>139208</v>
+        <v>138640</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>18223</v>
@@ -10872,10 +11087,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>173048</v>
+        <v>173005</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>71404</v>
+        <v>71361</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>101644</v>
@@ -10897,16 +11112,16 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>225946</v>
+        <v>225377</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>103392</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>122554</v>
+        <v>121985</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>52449</v>
+        <v>51881</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>9048</v>
@@ -10926,7 +11141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10950,7 +11165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 16 commande(s)</t>
+          <t>Épics créées ce mois — 18 commande(s)</t>
         </is>
       </c>
     </row>
@@ -11005,22 +11220,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35672</t>
+          <t>PDMDEP-35587</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35666</t>
+          <t>PDMDEP-35583</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -11030,7 +11245,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -11040,7 +11255,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00181382</t>
+          <t>00180931</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -11050,22 +11265,22 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35636</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35627</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANNEMASSE</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -11085,32 +11300,32 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00181182</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>0</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35606</t>
+          <t>PDMDEP-35532</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35597</t>
+          <t>PDMDEP-35518</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE PRIVAS</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -11123,39 +11338,31 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>00181049</t>
-        </is>
-      </c>
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr"/>
       <c r="I7" s="25" t="n">
-        <v>0</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35587</t>
+          <t>PDMDEP-35410</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35583</t>
+          <t>PDMDEP-35401</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -11165,7 +11372,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -11175,32 +11382,32 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00180931</t>
+          <t>00173074</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35532</t>
+          <t>PDMDEP-35606</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35518</t>
+          <t>PDMDEP-35597</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE PRIVAS</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -11213,31 +11420,39 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr"/>
-      <c r="H9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>00181049</t>
+        </is>
+      </c>
       <c r="I9" s="25" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -11257,32 +11472,32 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00180643</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>6285</v>
+        <v>28915.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35410</t>
+          <t>PDMDEP-35672</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35401</t>
+          <t>PDMDEP-35666</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -11302,32 +11517,32 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00173074</t>
+          <t>00181382</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35703</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35696</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t>COMMUNE DE HARFLEUR</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -11347,42 +11562,42 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00181438</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>28915.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35687</t>
+          <t>PDMDEP-35636</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35683</t>
+          <t>PDMDEP-35627</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>COMMUNE D'ANNEMASSE</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -11392,22 +11607,22 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00181396</t>
+          <t>00181182</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>2333.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35652</t>
+          <t>PDMDEP-35622</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35646</t>
+          <t>PDMDEP-35618</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -11417,7 +11632,7 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE GEX</t>
+          <t>Commune de la Roche-sur-Yon</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -11437,22 +11652,22 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00181167</t>
+          <t>00181123</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>6382.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35622</t>
+          <t>PDMDEP-35652</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35618</t>
+          <t>PDMDEP-35646</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
@@ -11462,7 +11677,7 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Roche-sur-Yon</t>
+          <t>VILLE DE GEX</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -11482,11 +11697,11 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00181123</t>
+          <t>00181167</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
-        <v>0</v>
+        <v>6382.5</v>
       </c>
     </row>
     <row r="16">
@@ -11582,22 +11797,22 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35511</t>
+          <t>PDMDEP-35687</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35504</t>
+          <t>PDMDEP-35683</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>[TEST]</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -11607,7 +11822,7 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
@@ -11617,32 +11832,32 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>0015489263</t>
+          <t>00181396</t>
         </is>
       </c>
       <c r="I18" s="26" t="n">
-        <v>0</v>
+        <v>2333.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35511</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35504</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>[TEST]</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -11652,7 +11867,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -11662,104 +11877,152 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>0015489263</t>
         </is>
       </c>
       <c r="I19" s="25" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-35464</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35460</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>00180631</t>
+        </is>
+      </c>
+      <c r="I20" s="26" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-35439</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-35435</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>03/09/2026</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>00180506</t>
         </is>
       </c>
-      <c r="I20" s="26" t="n">
+      <c r="I21" s="25" t="n">
         <v>3974</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>16 commande(s)</t>
-        </is>
-      </c>
-      <c r="I21" s="24" t="n">
-        <v>52730</v>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>dont Littéralis</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>8 commande(s)</t>
-        </is>
-      </c>
-      <c r="I22" s="24" t="n">
-        <v>14880</v>
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35719</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35715</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Commune de Dunkerque</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>00181457</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B23" s="17" t="n"/>
@@ -11770,10 +12033,52 @@
       <c r="G23" s="17" t="n"/>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>8 commande(s)</t>
+          <t>18 commande(s)</t>
         </is>
       </c>
       <c r="I23" s="24" t="n">
+        <v>52730</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>dont Littéralis</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="17" t="n"/>
+      <c r="H24" s="17" t="inlineStr">
+        <is>
+          <t>9 commande(s)</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="n">
+        <v>14880</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
+      <c r="G25" s="17" t="n"/>
+      <c r="H25" s="17" t="inlineStr">
+        <is>
+          <t>9 commande(s)</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="n">
         <v>37850</v>
       </c>
     </row>

--- a/jira_export_2026-09-14.xlsx
+++ b/jira_export_2026-09-14.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>206 h</t>
+          <t>213 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P132"/>
+  <dimension ref="A1:P135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -3377,7 +3377,7 @@
         <v>3</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>1242.9</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>621.45</v>
+        <v>497.16</v>
       </c>
     </row>
     <row r="38">
@@ -6689,7 +6689,7 @@
         <v>8</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>10</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0.95</v>
+        <v>1.15</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>10</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>0.95</v>
+        <v>1.15</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>10</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0.95</v>
+        <v>1.15</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>10</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0.95</v>
+        <v>1.15</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>10</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0.95</v>
+        <v>1.15</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>21</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="L115" s="11" t="inlineStr"/>
       <c r="M115" s="11" t="inlineStr"/>
@@ -9294,22 +9294,22 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-17710</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[Saint Lo] Migration</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Flavie BARDIN</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>Saint Lo</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9317,26 +9317,22 @@
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G121" s="11" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr"/>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>25/11/2024</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="K121" s="11" t="n">
         <v>0.5</v>
@@ -9356,22 +9352,22 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-16116</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>CD 01</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
@@ -9389,19 +9385,19 @@
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>3.58</v>
+        <v>0.25</v>
       </c>
       <c r="L122" s="14" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -9418,22 +9414,22 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9446,7 +9442,7 @@
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
@@ -9456,25 +9452,17 @@
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L123" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M123" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L123" s="11" t="inlineStr"/>
+      <c r="M123" s="11" t="inlineStr"/>
       <c r="N123" s="12" t="n">
         <v>0</v>
       </c>
@@ -9488,12 +9476,12 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
@@ -9503,7 +9491,7 @@
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9519,17 +9507,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H124" s="14" t="inlineStr"/>
+      <c r="H124" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>0.75</v>
+        <v>3.58</v>
       </c>
       <c r="L124" s="14" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -9546,12 +9538,12 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
@@ -9561,13 +9553,11 @@
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E125" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="n">
+        <v/>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
@@ -9576,7 +9566,7 @@
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr">
@@ -9586,17 +9576,25 @@
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L125" s="11" t="inlineStr"/>
-      <c r="M125" s="11" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L125" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M125" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N125" s="12" t="n">
         <v>0</v>
       </c>
@@ -9610,24 +9608,26 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C126" s="14" t="inlineStr"/>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C126" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E126" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="n">
+        <v/>
       </c>
       <c r="F126" s="14" t="inlineStr">
         <is>
@@ -9639,21 +9639,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H126" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H126" s="14" t="inlineStr"/>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>2.75</v>
+        <v>0.75</v>
       </c>
       <c r="L126" s="14" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -9670,21 +9666,27 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="C127" s="11" t="inlineStr"/>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E127" s="11" t="inlineStr"/>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="n">
+        <v/>
+      </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9692,27 +9694,35 @@
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H127" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K127" s="11" t="n">
         <v>0.25</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M127" s="11" t="inlineStr"/>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N127" s="12" t="n">
         <v>0</v>
       </c>
@@ -9726,21 +9736,29 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PSC-1334</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
-        </is>
-      </c>
-      <c r="C128" s="14" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C128" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
-        </is>
-      </c>
-      <c r="E128" s="14" t="inlineStr"/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E128" s="14" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
       <c r="F128" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9748,20 +9766,24 @@
       </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H128" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H128" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L128" s="14" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -9778,21 +9800,25 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr"/>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
-        </is>
-      </c>
-      <c r="E129" s="11" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9800,31 +9826,27 @@
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H129" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L129" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M129" s="11" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="L129" s="11" t="inlineStr"/>
+      <c r="M129" s="11" t="inlineStr"/>
       <c r="N129" s="12" t="n">
         <v>0</v>
       </c>
@@ -9838,18 +9860,18 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr"/>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E130" s="14" t="inlineStr"/>
@@ -9866,25 +9888,21 @@
       <c r="H130" s="14" t="inlineStr"/>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M130" s="14" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M130" s="14" t="inlineStr"/>
       <c r="N130" s="15" t="n">
         <v>0</v>
       </c>
@@ -9898,18 +9916,18 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PSC-668</t>
+          <t>PSC-1334</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr"/>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr"/>
@@ -9926,14 +9944,14 @@
       <c r="H131" s="11" t="inlineStr"/>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L131" s="11" t="inlineStr"/>
       <c r="M131" s="11" t="inlineStr"/>
@@ -9948,31 +9966,203 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="17" t="inlineStr">
+      <c r="A132" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1315</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE RANG DU FLIERS</t>
+        </is>
+      </c>
+      <c r="C132" s="14" t="inlineStr"/>
+      <c r="D132" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE RANG DU FLIERS</t>
+        </is>
+      </c>
+      <c r="E132" s="14" t="inlineStr"/>
+      <c r="F132" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G132" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H132" s="14" t="inlineStr"/>
+      <c r="I132" s="14" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="J132" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K132" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L132" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M132" s="14" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
+      <c r="N132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr"/>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr"/>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H133" s="11" t="inlineStr"/>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J133" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K133" s="11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L133" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N133" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="13" t="inlineStr">
+        <is>
+          <t>PSC-668</t>
+        </is>
+      </c>
+      <c r="B134" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="C134" s="14" t="inlineStr"/>
+      <c r="D134" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="E134" s="14" t="inlineStr"/>
+      <c r="F134" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G134" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H134" s="14" t="inlineStr"/>
+      <c r="I134" s="14" t="inlineStr">
+        <is>
+          <t>04/04/2025</t>
+        </is>
+      </c>
+      <c r="J134" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="K134" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L134" s="14" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+      <c r="N134" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B132" s="17" t="inlineStr"/>
-      <c r="C132" s="17" t="inlineStr"/>
-      <c r="D132" s="17" t="inlineStr"/>
-      <c r="E132" s="17" t="inlineStr"/>
-      <c r="F132" s="17" t="inlineStr"/>
-      <c r="G132" s="17" t="inlineStr"/>
-      <c r="H132" s="17" t="inlineStr"/>
-      <c r="I132" s="17" t="inlineStr"/>
-      <c r="J132" s="17" t="inlineStr"/>
-      <c r="K132" s="17" t="inlineStr"/>
-      <c r="L132" s="17" t="inlineStr"/>
-      <c r="M132" s="17" t="inlineStr"/>
-      <c r="N132" s="18" t="n">
+      <c r="B135" s="17" t="inlineStr"/>
+      <c r="C135" s="17" t="inlineStr"/>
+      <c r="D135" s="17" t="inlineStr"/>
+      <c r="E135" s="17" t="inlineStr"/>
+      <c r="F135" s="17" t="inlineStr"/>
+      <c r="G135" s="17" t="inlineStr"/>
+      <c r="H135" s="17" t="inlineStr"/>
+      <c r="I135" s="17" t="inlineStr"/>
+      <c r="J135" s="17" t="inlineStr"/>
+      <c r="K135" s="17" t="inlineStr"/>
+      <c r="L135" s="17" t="inlineStr"/>
+      <c r="M135" s="17" t="inlineStr"/>
+      <c r="N135" s="18" t="n">
         <v>48290.375</v>
       </c>
-      <c r="O132" s="18" t="n">
+      <c r="O135" s="18" t="n">
         <v>23785.268</v>
       </c>
-      <c r="P132" s="18" t="n">
-        <v>201.06</v>
+      <c r="P135" s="18" t="n">
+        <v>194.48</v>
       </c>
     </row>
   </sheetData>
@@ -10105,6 +10295,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10916,16 +11109,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>63.17</v>
+        <v>65.67</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>19.17</v>
+        <v>20.17</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>10</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>92.33</v>
+        <v>95.83</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>17.92</v>
@@ -10935,7 +11128,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -10977,7 +11170,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>62</v>
+        <v>65.5</v>
       </c>
     </row>
   </sheetData>
